--- a/docs/triton-learning/cards/triton-lesson-09-persistent-matmul-oral.xlsx
+++ b/docs/triton-learning/cards/triton-lesson-09-persistent-matmul-oral.xlsx
@@ -36,22 +36,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">请用约 60–90 秒向面试官讲清：持久化矩阵乘与逐 tile 发射相比改了什么、省掉了什么？Triton 的 flatten 又在此基础上做了什么、代价是什么？怎样确认它生效了？</t>
+          <t xml:space="preserve">请用约 60–90 秒向面试官讲清：持久化矩阵乘与逐 tile 发射相比改了什么、省掉了什么？Triton 3.7.1 的 flatten 又在此基础上做了什么、代价是什么？怎样确认它生效了？</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
           <t xml:space="preserve">[T#B,!36b59d#结论]：持久化只发射每个 SM 一个 CTA，在 kernel 里按步长循环领取 tile，省掉重复的 CTA 发射与退出；flatten 再把 tile 循环和 K 循环合成一层，让软件流水跨过 tile 边界。
-• [T#B#为何需要]：块大时一个 SM 只放得下一个 CTA，tile 之间的固定成本没有别的 CTA 掩盖，就是张量核心的空档。
-• [T#B#调度]：步长必须等于发射的 CTA 数，否则结果正确但重复计算；可以用 tl.num_programs(0) 取。
-• [T#B#flatten]：流水的预热与排空从每 tile 一次变成每 CTA 一次，下一个 tile 的读入在当前 tile 算完前就发出；写回仍是每 tile 一次。
-• [T#B#代价与确认]：写回中转不能借用输入槽，共享内存多一档；合并条件不满足时静默忽略，要看 TTGIR 里的 scf.if、共享内存和排空的位置。
-[T#B,!c47f17#边界]：只加持久循环不会让 tile 之间重叠；flatten 是请求，不是保证。</t>
+• [T#B#调度]：步长必须等于发射的 CTA 数，网格比步长大时，同一个 tile 会被几个 CTA 重复计算；可以用 tl.num_programs(0) 取步长。
+• [T#B#flatten]：流水的预热与排空从每 tile 一次变成每 CTA 一次，下一个 tile 的读入在当前 tile 算完前就发出；tile 的 prologue 与 epilogue 仍是每 tile 一次。
+• [T#B#代价]：epilogue 换布局用的中转借不到仍被占着的输入槽，共享内存多一档。
+• [T#B#确认]：合并条件不满足时静默忽略；在 NVIDIA 后端上看 TTGIR 里是否出现 scf.if、排空的等待是否移出循环，共享内存只作辅助。
+[T#B,!c47f17#边界]：只加持久循环不会让 tile 之间重叠；合并发生了也不等于有提前量，要看 ttg.async_wait 的 num。</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">说出每个 SM 一个 CTA、以发射的 CTA 数为步长领取 tile；说出持久化直接省掉的是发射与退出，重叠要靠 flatten 或专用化；说清 flatten 省掉预热排空、省不掉写回；说出共享内存多一档的原因；给出确认合并生效的产物证据</t>
+          <t xml:space="preserve">说出每个 SM 一个 CTA、以发射的 CTA 数为步长领取 tile；说出持久化直接省掉的是发射与退出，重叠要靠 flatten 或专用化；说清 flatten 省掉预热排空、省不掉 tile 的 prologue 与 epilogue；说出共享内存多一档的原因；给出确认合并生效的产物证据，以 scf.if 为主</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -63,22 +63,22 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">请用约 60–90 秒讲清：同一个 Triton 矩阵乘在 sm_89、sm_90、sm_100 和 sm_120 上，搬数据和算乘加分别由谁完成？为什么新硬件让数据离开寄存器？warp 专用化在其中解决什么？</t>
+          <t xml:space="preserve">请用约 60–90 秒向面试官讲清：同一个 Triton 3.7.1 矩阵乘在 sm_89、sm_90、sm_100 和 sm_120 上，正在被乘加用的操作数和累加器各放在哪里？为什么新硬件让数据离开线程的寄存器，代价是什么？warp 专用化在其中解决什么？</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：趋势是张量核心越来越不依赖线程：sm_89 与 sm_120 由线程把操作数取进寄存器、按 warp 发 mma.sync；sm_90 的 wgmma 按 warpgroup 直接读共享内存；sm_100 的 tcgen05.mma 由一个线程发起，累加器放进 TMEM。
-• [T#B#槽数]：操作数留在共享内存时槽要占到乘加完成，每个操作数多一个槽，寄存器则省下来。
-• [T#B#为什么]：寄存器私有且有上限，线程要逐条喂指令，计算绑在持有数据的线程上；把数据移出寄存器是为了解放线程。
-• [T#B#布局]：乘加指令要沿 K 连续的操作数，所以 B 常按 \[N, K\] 存放；fp8 必须如此。
-• [T#B#专用化]：flatten 只在一条执行顺序里挪先后，专用化另开一批 warp 专门搬运，代价是更多 warp、屏障和缓冲。
-[T#B,!c47f17#边界]：sm_120 是新一代却仍用 mma.sync；各项改进贡献多少性能需要实测。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：趋势是让张量核心越来越不依赖线程：sm_89 与 sm_120 的 mma.sync 要线程把操作数取进寄存器，累加器也在寄存器里；sm_90 的 wgmma 直接读共享内存里的操作数；sm_100 的 tcgen05 再把累加器放进 TMEM。
+• [T#B#槽数]：操作数留在共享内存时，槽要占到乘加完成，同样 num_stages 下每个操作数多一个槽，寄存器则省下来；提前量不变。
+• [T#B#为什么]：寄存器按线程私有且有上限，线程要逐条指令喂张量核心，计算绑在持有数据的线程上；把数据移出寄存器是为了解放线程。
+• [T#B#代价]：输入槽被占得更久、写回要在共享内存里中转，共享内存上限低的设备更受制约。
+• [T#B#专用化]：flatten 只在一条执行顺序里挪先后，专用化另开一批 warp 专门搬运，代价是更多 warp、屏障和输入缓冲。
+[T#B,!c47f17#边界]：sm_120 是新一代却仍用 mma.sync；各项改进各贡献多少性能需要实测。</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">四种目标各说对乘加的执行者与操作数的位置；解释 sm_90 多一个输入槽的原因；给出让数据离开寄存器的至少两条理由；说出 B 按 \[N, K\] 存放的理由；区分 flatten 与专用化</t>
+          <t xml:space="preserve">四种目标各说对操作数与累加器的位置；解释操作数就地读时同样 num_stages 下多一个输入槽、寄存器变少；给出让数据离开寄存器的至少两条理由；区分 flatten 与专用化，并说出专用化的代价</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -90,14 +90,14 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">请用约 60–90 秒讲清：B 按行主序 \[K, N\] 存放时，怎样让 Triton 持久化矩阵乘中 B 的读入在 flatten 开与关时都是 16 字节、提前发出的异步拷贝？并说出你会怎样诊断。</t>
+          <t xml:space="preserve">请用约 60–90 秒向面试官讲清：在 Triton 3.7.1 中，B 按行主序 \[K, N\] 存放时，怎样让持久化矩阵乘中 B 的读入在 flatten 开与关时都是 16 字节、提前发出的异步拷贝？并说出你会怎样诊断。</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
           <t xml:space="preserve">[T#B,!36b59d#结论]：关键是让编译器在 B 的连续方向 N 上看得出取值连续和对齐，并且这条信息出现在流水看得到的地方。
 • [T#B#越界处理]：tl.where 把越界下标改成 0 会让取值连续度降到 1；要么只用 mask、不改写，要么改写后用 max_contiguous 和 multiple_of 两条声明补回。
-• [T#B#合并后]：flatten 开时，tile 开头算的值经 scf.if 传出会丢掉声明，所以 N 方向的下标要在 K 循环里计算。
+• [T#B#合并后]：flatten 开时，tile 开头算的值经 scf.if 传出会丢掉声明，所以 N 方向的下标要在 K 循环里计算，写回时再另算一份。
 • [T#B#安全性]：声明在边界 tile 里不成立，但只发生在用不到的组里：对齐前提、组间边界、越界值被 mask 或丢弃。
 • [T#B#诊断]：TTGIR 里没有 fp16 的同步 tt.load、PTX 的 cp.async 都是 16 字节，并且循环里 ttg.async_wait 的 num 大于 0。
 [T#B,!c47f17#边界]：N 不是 16 的倍数时行首对不齐，怎么声明都只能逐元素读。</t>
@@ -117,14 +117,14 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">请用约 60–90 秒讲清：你怎样在 RTX 5090 上检验“持久化的优势随 K 增大而减小”这个预测？结果说明了什么，又没有说明什么？</t>
+          <t xml:space="preserve">请用约 60–90 秒向面试官讲清：你怎样在 RTX 5090 上用 Triton 3.7.1 检验“持久化的优势随 K 增大而减小”这个预测？结果说明了什么，又没有说明什么？</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
           <t xml:space="preserve">[T#B,!36b59d#结论]：用同一个 kernel 只改调度和 flatten 两个开关，交替测量、轮内相除、判据先写；结果支持方向，但收益主要来自 flatten，持久化本身很小。
-• [T#B#设置]：块 128 × 128 × 64、3 个 stage、8 个 warp，M = N = 8192，K 取 128、512、2048；逐 tile 4096 个 CTA，持久 170 个。
-• [T#B#结果]：持久化本身 1.023、1.002、1.000；flatten 1.184、1.035、0.987；总比值 1.213、1.037、0.987，随 K 下降。
+• [T#B#设置]：块 128 × 128 × 64 固定、M = N = 8192，K 从 128 扫到 2048；逐 tile 版每个 CTA 一个 tile，持久版每个 SM 一个 CTA。
+• [T#B#结果]：持久化本身最多 2.3%；flatten 在 K = 128 时约 18%，到 K = 2048 成了净代价；总比值随 K 下降。
 • [T#B#解读]：“省掉重复发射”只得到很弱的支持；持久化本身那一列含分派、固定工作和调度方式三项，分不开。
 [T#B,!c47f17#边界]：只测了一张卡、一组配置；K = 2048 时 flatten 的代价来源没有验证。</t>
         </is>
